--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1705,7 +1705,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 11 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 16 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3263,7 +3263,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="237">
   <si>
     <t xml:space="preserve">UAE Freelancer &amp; Small Business Bookkeeping Tracker 2026</t>
   </si>
@@ -279,7 +279,7 @@
     <t xml:space="preserve">Standard VAT rate</t>
   </si>
   <si>
-    <t xml:space="preserve">UAE standard rate. Source: Federal Decree-Law No. 8 of 2017, tax.gov.ae</t>
+    <t xml:space="preserve">UAE standard rate. Source: Federal Decree-Law No. 8 of 2017, tax.gov.ae; checked 2026-09-17.</t>
   </si>
   <si>
     <t xml:space="preserve">Product sales</t>
@@ -294,7 +294,7 @@
     <t xml:space="preserve">VAT mandatory registration threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">Taxable supplies in past 12 months (or expected next 30 days).</t>
+    <t xml:space="preserve">Taxable supplies in past 12 months (or expected in the next 30 days) - a rolling test, not a year-end one. Unchanged for 2026; checked 2026-09-17.</t>
   </si>
   <si>
     <t xml:space="preserve">Commission</t>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t xml:space="preserve">VAT voluntary registration threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional registration is available from this level of supplies or taxable expenses. Unchanged for 2026; checked 2026-09-17.</t>
   </si>
   <si>
     <t xml:space="preserve">Training</t>
@@ -318,7 +321,7 @@
     <t xml:space="preserve">Corporate Tax rate</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: Federal Decree-Law No. 47 of 2022.</t>
+    <t xml:space="preserve">Source: Federal Decree-Law No. 47 of 2022; checked 2026-09-17.</t>
   </si>
   <si>
     <t xml:space="preserve">Other income</t>
@@ -330,7 +333,7 @@
     <t xml:space="preserve">Corporate Tax 0% band (taxable income)</t>
   </si>
   <si>
-    <t xml:space="preserve">Taxable income up to this amount is taxed at 0%.</t>
+    <t xml:space="preserve">Taxable income up to this amount is taxed at 0%. Source: Federal Decree-Law No. 47 of 2022; checked 2026-09-17.</t>
   </si>
   <si>
     <t xml:space="preserve">Bank &amp; payment fees</t>
@@ -349,6 +352,9 @@
   </si>
   <si>
     <t xml:space="preserve">Small Business Relief revenue threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue, not profit - the test is turnover. Source: Ministerial Decision 73 of 2023; checked 2026-09-17.</t>
   </si>
   <si>
     <t xml:space="preserve">Contractors &amp; salaries</t>
@@ -1705,7 +1711,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 16 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 17 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2842,7 +2848,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>77</v>
       </c>
@@ -2862,7 +2868,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
         <v>82</v>
       </c>
@@ -2879,199 +2885,203 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
         <v>86</v>
       </c>
       <c r="B9" s="30" t="n">
         <v>187500</v>
       </c>
-      <c r="C9" s="24"/>
+      <c r="C9" s="24" t="s">
+        <v>87</v>
+      </c>
       <c r="E9" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" s="29" t="n">
         <v>0.09</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" s="30" t="n">
         <v>375000</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" s="28" t="s">
         <v>72</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13" s="30" t="n">
         <v>3000000</v>
       </c>
-      <c r="C13" s="24"/>
+      <c r="C13" s="24" t="s">
+        <v>103</v>
+      </c>
       <c r="F13" s="25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B14" s="33" t="n">
         <v>47483</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B15" s="27" t="n">
         <v>46023</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B16" s="27" t="n">
         <v>46112</v>
       </c>
       <c r="C16" s="24"/>
       <c r="F16" s="25" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B17" s="34" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G17" s="32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B18" s="35" t="n">
         <v>30</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E19" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B20" s="36"/>
       <c r="E20" s="32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B21" s="36"/>
       <c r="E21" s="32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E22" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3112,62 +3122,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>59</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3175,13 +3185,13 @@
         <v>46034</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E4" s="36" t="s">
         <v>63</v>
@@ -3201,7 +3211,7 @@
         <v>12600</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K4" s="37" t="n">
         <v>46050</v>
@@ -3231,13 +3241,13 @@
         <v>46056</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>68</v>
@@ -3257,13 +3267,13 @@
         <v>4725</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K5" s="37"/>
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>
@@ -3283,13 +3293,13 @@
         <v>46073</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>68</v>
@@ -3309,7 +3319,7 @@
         <v>8000</v>
       </c>
       <c r="J6" s="36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K6" s="37" t="n">
         <v>46086</v>
@@ -21288,56 +21298,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21345,10 +21355,10 @@
         <v>46027</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>75</v>
@@ -21364,7 +21374,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I4" s="39" t="n">
         <f aca="false">IF(E4="","",IF(AND(H4="Yes",F4="Standard 5%"),G4,0))</f>
@@ -21375,7 +21385,7 @@
         <v>7500</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L4" s="36" t="s">
         <v>72</v>
@@ -21394,10 +21404,10 @@
         <v>46037</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>64</v>
@@ -21424,7 +21434,7 @@
         <v>2520</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L5" s="36" t="s">
         <v>72</v>
@@ -21443,10 +21453,10 @@
         <v>46061</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>69</v>
@@ -21473,7 +21483,7 @@
         <v>1575</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L6" s="36" t="s">
         <v>72</v>
@@ -36946,17 +36956,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C4" s="41" t="n">
         <f aca="false">VP_START</f>
@@ -36965,7 +36975,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C5" s="41" t="n">
         <f aca="false">VP_END</f>
@@ -36974,7 +36984,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C6" s="42" t="str">
         <f aca="false">Settings!B6</f>
@@ -36983,27 +36993,27 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">SUMIFS(Income!$F$4:$F$503,Income!$G$4:$G$503,"Standard 5%",Income!$P$4:$P$503,1)</f>
@@ -37014,15 +37024,15 @@
         <v>825</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">SUMIFS(Income!$F$4:$F$503,Income!$G$4:$G$503,"Zero-rated 0%",Income!$P$4:$P$503,1)</f>
@@ -37033,15 +37043,15 @@
         <v>0</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C11" s="39" t="n">
         <f aca="false">SUMIFS(Income!$F$4:$F$503,Income!$G$4:$G$503,"Exempt",Income!$P$4:$P$503,1)</f>
@@ -37052,15 +37062,15 @@
         <v>0</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">SUMIFS(Income!$F$4:$F$503,Income!$G$4:$G$503,"Out of scope",Income!$P$4:$P$503,1)</f>
@@ -37071,15 +37081,15 @@
         <v>0</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C13" s="44" t="n">
         <f aca="false">C9+C10+C11</f>
@@ -37090,15 +37100,15 @@
         <v>825</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">SUMIFS(Expenses!$E$4:$E$503,Expenses!$H$4:$H$503,"Yes",Expenses!$F$4:$F$503,"Standard 5%",Expenses!$N$4:$N$503,1)</f>
@@ -37109,15 +37119,15 @@
         <v>195</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C15" s="44" t="n">
         <f aca="false">C14</f>
@@ -37131,10 +37141,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="46" t="n">
@@ -37142,12 +37152,12 @@
         <v>630</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D17" s="47" t="n">
         <f aca="false">SUMIFS(Income!$F$4:$F$503,Income!$P$4:$P$503,1)-C9-C10-C11-C12</f>
@@ -37156,7 +37166,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D18" s="48" t="n">
         <f aca="false">SUMIFS(Expenses!$G$4:$G$503,Expenses!$N$4:$N$503,1)-D14</f>
@@ -37165,7 +37175,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D19" s="47" t="n">
         <f aca="false">SUMIFS(Expenses!$E$4:$E$503,Expenses!$N$4:$N$503,1)-SUMIFS(Expenses!$E$4:$E$503,Expenses!$F$4:$F$503,"Standard 5%",Expenses!$N$4:$N$503,1)-SUMIFS(Expenses!$E$4:$E$503,Expenses!$F$4:$F$503,"Zero-rated 0%",Expenses!$N$4:$N$503,1)-SUMIFS(Expenses!$E$4:$E$503,Expenses!$F$4:$F$503,"Exempt",Expenses!$N$4:$N$503,1)-SUMIFS(Expenses!$E$4:$E$503,Expenses!$F$4:$F$503,"Out of scope",Expenses!$N$4:$N$503,1)</f>
@@ -37174,7 +37184,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D20" s="48" t="n">
         <f aca="true">SUMIFS(Income!$F$4:$F$503,Income!$G$4:$G$503,"Standard 5%",Income!$A$4:$A$503,"&gt;"&amp;(TODAY()-365))+SUMIFS(Income!$F$4:$F$503,Income!$G$4:$G$503,"Zero-rated 0%",Income!$A$4:$A$503,"&gt;"&amp;(TODAY()-365))</f>
@@ -37183,7 +37193,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D21" s="49" t="str">
         <f aca="false">IF(D20&gt;=VAT_MAND,"ABOVE MANDATORY THRESHOLD — must be registered",IF(D20&gt;=VAT_VOL,"Above voluntary threshold — may register","Below voluntary threshold"))</f>
@@ -37192,7 +37202,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="50"/>
@@ -37237,147 +37247,147 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B4" s="51" t="str">
         <f aca="false">TEXT(FY_START,"dd-mmm-yyyy")&amp;" to "&amp;TEXT(EDATE(FY_START,12)-1,"dd-mmm-yyyy")</f>
         <v>01-Jan-2026 to 31-Dec-2026</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B5" s="52" t="n">
         <f aca="false">SUMIFS(Income!$F$4:$F$503,Income!$A$4:$A$503,"&gt;="&amp;FY_START,Income!$A$4:$A$503,"&lt;="&amp;EDATE(FY_START,12)-1)</f>
         <v>24500</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B6" s="52" t="n">
         <f aca="false">SUMIFS(Expenses!$E$4:$E$503,Expenses!$L$4:$L$503,"Yes",Expenses!$A$4:$A$503,"&gt;="&amp;FY_START,Expenses!$A$4:$A$503,"&lt;="&amp;EDATE(FY_START,12)-1)</f>
         <v>11400</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B7" s="52" t="n">
         <f aca="false">SUMIFS(Expenses!$G$4:$G$503,Expenses!$L$4:$L$503,"Yes",Expenses!$H$4:$H$503,"No",Expenses!$A$4:$A$503,"&gt;="&amp;FY_START,Expenses!$A$4:$A$503,"&lt;="&amp;EDATE(FY_START,12)-1)</f>
         <v>0</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B8" s="53" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B9" s="52" t="n">
         <f aca="false">B5-B6-B7+B8</f>
         <v>13100</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B10" s="51" t="str">
         <f aca="false">SBR_ELECT</f>
         <v>Yes</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B11" s="51" t="str">
         <f aca="false">IF(AND(SBR_ELECT="Yes",B5&lt;=SBR_LIMIT,EDATE(FY_START,12)-1&lt;=SBR_END),"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B12" s="52" t="n">
         <f aca="false">MAX(0,B9-CT_BAND)</f>
         <v>0</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B13" s="54" t="n">
         <f aca="false">IF(B11="Yes",0,B12*CT_RATE)</f>
         <v>0</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B14" s="55" t="n">
         <f aca="false">IF(B9&lt;=0,0,B13/B9)</f>
@@ -37387,19 +37397,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B15" s="52" t="n">
         <f aca="false">B13/12</f>
         <v>0</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1711,7 +1711,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 17 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 18 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3273,7 +3273,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1711,7 +1711,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 18 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 20 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3273,7 +3273,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1711,7 +1711,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 20 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 21 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3273,7 +3273,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1711,7 +1711,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 21 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 22 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3273,7 +3273,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1711,7 +1711,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 22 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 23 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3273,7 +3273,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>
